--- a/backend/test_import_formations_seances.xlsx
+++ b/backend/test_import_formations_seances.xlsx
@@ -20,10 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="HH:MM"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="HH:MM"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -99,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -131,19 +130,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,6 +153,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -539,661 +550,591 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Formation (cycle)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Formation</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Module (titre)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Objectif</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Lieu</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Date début</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Date fin</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Volume horaire (h)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Groupe</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vague</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Programme</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Rédaction Administrative</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Maîtriser la rédaction des actes administratifs</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>2026-05-09 17:00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="G2" t="n">
         <v>40</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Droit Administratif</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Connaître le cadre juridique de l'administration publique</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-12 08:00</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-16 17:00</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="G3" t="n">
         <v>40</v>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Finances Publiques</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Comprendre les mécanismes des finances publiques</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-05-19 08:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2026-05-22 17:00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="G4" t="n">
         <v>30</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Rédaction Administrative</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Maîtriser la rédaction des actes administratifs</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-05-09 17:00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="G5" t="n">
         <v>40</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Droit Administratif</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Connaître le cadre juridique de l'administration publique</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2026-05-12 08:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-05-16 17:00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="G6" t="n">
         <v>40</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Management des Administrations Publiques</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Développer les capacités manégariales des agents publics</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2026-06-02 08:00</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-06-06 17:00</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="G7" t="n">
         <v>40</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Culture Civique</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Renforcer la culture civique et institutionnelle</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026-06-09 08:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-06-10 17:00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="G8" t="n">
         <v>16</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Commande Publique</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Maîtriser les procédures de passation des marchés</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-05-09 17:00</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="G9" t="n">
         <v>40</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bureautique et Outils Numériques</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Utiliser les outils bureautiques courants</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026-05-12 08:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-05-15 17:00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="G10" t="n">
         <v>30</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>FORMATION EN ADMINISTRATION DE BASE</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Gestion des Ressources Humaines</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Comprendre les fondements de la GRH publique</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-05-08 17:00</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="G11" t="n">
         <v>32</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1573,88 +1514,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>FNCP26-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>KOUAME</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Jean-Marc</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>MASCULIN</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>15/03/1990</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Abidjan</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>A4/GROUPE 1</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Concours direct</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>Administrateur Civil</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>jm.kouame@gouv.ci</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>0701001001</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr"/>
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>SALLE A</t>
         </is>
@@ -1759,88 +1700,88 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>FNCP26-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>BAMBA</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Oumar</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>MASCULIN</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>05/11/1988</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Korhogo</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>A4/GROUPE 2</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Concours direct</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Administrateur Civil</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>bamba.o@gouv.ci</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>0703003003</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>SALLE B</t>
         </is>
@@ -1945,88 +1886,88 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>FNCP26-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>COULIBALY</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Mamadou</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>MASCULIN</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30/01/1985</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Man</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>A3/GROUPE 1</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>Concours professionnel</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>Attaché Administration</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>coulibaly.m@gouv.ci</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>0705005005</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>SALLE C</t>
         </is>
@@ -2131,88 +2072,88 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>FNCP26-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>TOURE</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Ibrahim</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>MASCULIN</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>08/04/1991</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Yamoussoukro</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>B3/GROUPE 1</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Concours direct</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>Agent administratif</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>toure.i@gouv.ci</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>0707007007</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>SALLE D</t>
         </is>
@@ -2391,7 +2332,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="19" t="n">
         <v>46147</v>
       </c>
       <c r="D2" s="10" t="n">
@@ -2402,10 +2343,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2420,7 +2361,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="21" t="n">
         <v>46147</v>
       </c>
       <c r="D3" s="13" t="n">
@@ -2431,10 +2372,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2449,7 +2390,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="19" t="n">
         <v>46148</v>
       </c>
       <c r="D4" s="10" t="n">
@@ -2460,10 +2401,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2478,7 +2419,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="21" t="n">
         <v>46148</v>
       </c>
       <c r="D5" s="13" t="n">
@@ -2489,10 +2430,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2507,7 +2448,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="19" t="n">
         <v>46149</v>
       </c>
       <c r="D6" s="10" t="n">
@@ -2518,10 +2459,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2536,7 +2477,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="21" t="n">
         <v>46149</v>
       </c>
       <c r="D7" s="13" t="n">
@@ -2547,10 +2488,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2565,7 +2506,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="19" t="n">
         <v>46154</v>
       </c>
       <c r="D8" s="10" t="n">
@@ -2576,10 +2517,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2594,7 +2535,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="21" t="n">
         <v>46154</v>
       </c>
       <c r="D9" s="13" t="n">
@@ -2605,10 +2546,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2623,7 +2564,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="19" t="n">
         <v>46155</v>
       </c>
       <c r="D10" s="10" t="n">
@@ -2634,10 +2575,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2652,7 +2593,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="21" t="n">
         <v>46155</v>
       </c>
       <c r="D11" s="13" t="n">
@@ -2663,10 +2604,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2681,7 +2622,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="19" t="n">
         <v>46156</v>
       </c>
       <c r="D12" s="10" t="n">
@@ -2692,10 +2633,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2710,7 +2651,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="21" t="n">
         <v>46156</v>
       </c>
       <c r="D13" s="13" t="n">
@@ -2721,10 +2662,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2739,7 +2680,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="19" t="n">
         <v>46161</v>
       </c>
       <c r="D14" s="10" t="n">
@@ -2750,10 +2691,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2768,7 +2709,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="21" t="n">
         <v>46161</v>
       </c>
       <c r="D15" s="13" t="n">
@@ -2779,10 +2720,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2797,7 +2738,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="19" t="n">
         <v>46162</v>
       </c>
       <c r="D16" s="10" t="n">
@@ -2808,10 +2749,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2826,7 +2767,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="21" t="n">
         <v>46162</v>
       </c>
       <c r="D17" s="13" t="n">
@@ -2837,10 +2778,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2855,7 +2796,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="19" t="n">
         <v>46147</v>
       </c>
       <c r="D18" s="10" t="n">
@@ -2866,10 +2807,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2884,7 +2825,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="21" t="n">
         <v>46147</v>
       </c>
       <c r="D19" s="13" t="n">
@@ -2895,10 +2836,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2913,7 +2854,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="19" t="n">
         <v>46148</v>
       </c>
       <c r="D20" s="10" t="n">
@@ -2924,10 +2865,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2942,7 +2883,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="21" t="n">
         <v>46148</v>
       </c>
       <c r="D21" s="13" t="n">
@@ -2953,10 +2894,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -2971,7 +2912,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="19" t="n">
         <v>46149</v>
       </c>
       <c r="D22" s="10" t="n">
@@ -2982,10 +2923,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3000,7 +2941,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="21" t="n">
         <v>46149</v>
       </c>
       <c r="D23" s="13" t="n">
@@ -3011,10 +2952,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3029,7 +2970,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="19" t="n">
         <v>46154</v>
       </c>
       <c r="D24" s="10" t="n">
@@ -3040,10 +2981,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3058,7 +2999,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="21" t="n">
         <v>46154</v>
       </c>
       <c r="D25" s="13" t="n">
@@ -3069,10 +3010,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F25" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3087,7 +3028,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="19" t="n">
         <v>46155</v>
       </c>
       <c r="D26" s="10" t="n">
@@ -3098,10 +3039,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3116,7 +3057,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="21" t="n">
         <v>46155</v>
       </c>
       <c r="D27" s="13" t="n">
@@ -3127,10 +3068,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3145,7 +3086,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="19" t="n">
         <v>46156</v>
       </c>
       <c r="D28" s="10" t="n">
@@ -3156,10 +3097,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3174,7 +3115,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="21" t="n">
         <v>46156</v>
       </c>
       <c r="D29" s="13" t="n">
@@ -3185,10 +3126,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F29" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3203,7 +3144,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C30" s="19" t="n">
         <v>46175</v>
       </c>
       <c r="D30" s="10" t="n">
@@ -3214,10 +3155,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3232,7 +3173,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="21" t="n">
         <v>46175</v>
       </c>
       <c r="D31" s="13" t="n">
@@ -3243,10 +3184,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F31" s="15" t="n">
+      <c r="F31" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3261,7 +3202,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="19" t="n">
         <v>46176</v>
       </c>
       <c r="D32" s="10" t="n">
@@ -3272,10 +3213,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3290,7 +3231,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="21" t="n">
         <v>46176</v>
       </c>
       <c r="D33" s="13" t="n">
@@ -3301,10 +3242,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F33" s="15" t="n">
+      <c r="F33" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3319,7 +3260,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C34" s="19" t="n">
         <v>46177</v>
       </c>
       <c r="D34" s="10" t="n">
@@ -3330,10 +3271,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3348,7 +3289,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C35" s="21" t="n">
         <v>46177</v>
       </c>
       <c r="D35" s="13" t="n">
@@ -3359,10 +3300,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F35" s="15" t="n">
+      <c r="F35" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3377,7 +3318,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C36" s="11" t="n">
+      <c r="C36" s="19" t="n">
         <v>46182</v>
       </c>
       <c r="D36" s="10" t="n">
@@ -3388,10 +3329,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G36" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3406,7 +3347,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="21" t="n">
         <v>46182</v>
       </c>
       <c r="D37" s="13" t="n">
@@ -3417,10 +3358,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F37" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3435,7 +3376,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C38" s="11" t="n">
+      <c r="C38" s="19" t="n">
         <v>46183</v>
       </c>
       <c r="D38" s="10" t="n">
@@ -3446,10 +3387,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3464,7 +3405,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="21" t="n">
         <v>46183</v>
       </c>
       <c r="D39" s="13" t="n">
@@ -3475,10 +3416,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F39" s="15" t="n">
+      <c r="F39" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3493,7 +3434,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C40" s="19" t="n">
         <v>46147</v>
       </c>
       <c r="D40" s="10" t="n">
@@ -3504,10 +3445,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3522,7 +3463,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C41" s="14" t="n">
+      <c r="C41" s="21" t="n">
         <v>46147</v>
       </c>
       <c r="D41" s="13" t="n">
@@ -3533,10 +3474,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="F41" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3551,7 +3492,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C42" s="11" t="n">
+      <c r="C42" s="19" t="n">
         <v>46148</v>
       </c>
       <c r="D42" s="10" t="n">
@@ -3562,10 +3503,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F42" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3580,7 +3521,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
+      <c r="C43" s="21" t="n">
         <v>46148</v>
       </c>
       <c r="D43" s="13" t="n">
@@ -3591,10 +3532,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F43" s="15" t="n">
+      <c r="F43" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3609,7 +3550,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C44" s="19" t="n">
         <v>46149</v>
       </c>
       <c r="D44" s="10" t="n">
@@ -3620,10 +3561,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F44" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G44" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3638,7 +3579,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C45" s="14" t="n">
+      <c r="C45" s="21" t="n">
         <v>46149</v>
       </c>
       <c r="D45" s="13" t="n">
@@ -3649,10 +3590,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F45" s="15" t="n">
+      <c r="F45" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3667,7 +3608,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C46" s="19" t="n">
         <v>46154</v>
       </c>
       <c r="D46" s="10" t="n">
@@ -3678,10 +3619,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G46" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3696,7 +3637,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C47" s="14" t="n">
+      <c r="C47" s="21" t="n">
         <v>46154</v>
       </c>
       <c r="D47" s="13" t="n">
@@ -3707,10 +3648,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F47" s="15" t="n">
+      <c r="F47" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3725,7 +3666,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="19" t="n">
         <v>46155</v>
       </c>
       <c r="D48" s="10" t="n">
@@ -3736,10 +3677,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F48" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="G48" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3754,7 +3695,7 @@
           <t>GROUPE 1</t>
         </is>
       </c>
-      <c r="C49" s="14" t="n">
+      <c r="C49" s="21" t="n">
         <v>46155</v>
       </c>
       <c r="D49" s="13" t="n">
@@ -3765,10 +3706,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F49" s="15" t="n">
+      <c r="F49" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3783,7 +3724,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n">
+      <c r="C50" s="19" t="n">
         <v>46147</v>
       </c>
       <c r="D50" s="10" t="n">
@@ -3794,10 +3735,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="F50" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G50" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3812,7 +3753,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="21" t="n">
         <v>46147</v>
       </c>
       <c r="D51" s="13" t="n">
@@ -3823,10 +3764,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F51" s="15" t="n">
+      <c r="F51" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3841,7 +3782,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="19" t="n">
         <v>46148</v>
       </c>
       <c r="D52" s="10" t="n">
@@ -3852,10 +3793,10 @@
           <t>Matin</t>
         </is>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="F52" s="20" t="n">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="G52" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3870,7 +3811,7 @@
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="C53" s="14" t="n">
+      <c r="C53" s="21" t="n">
         <v>46148</v>
       </c>
       <c r="D53" s="13" t="n">
@@ -3881,10 +3822,10 @@
           <t>Après-midi</t>
         </is>
       </c>
-      <c r="F53" s="15" t="n">
+      <c r="F53" s="22" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="22" t="n">
         <v>0.7291666666666666</v>
       </c>
     </row>
@@ -3937,7 +3878,7 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>Formation (cycle), Module (titre), Date début, Date fin, Catégorie</t>
+          <t>Formation, Module (titre), Site, Date début, Date fin, Volume horaire (h), Catégorie, Grade, Groupe, Vague</t>
         </is>
       </c>
     </row>

--- a/backend/test_import_formations_seances.xlsx
+++ b/backend/test_import_formations_seances.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -572,35 +572,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Bâtiment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Salle</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Date début</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Date fin</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Volume horaire (h)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Groupe</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Vague</t>
         </is>
@@ -625,35 +635,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-05-09 17:00</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>40</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -678,35 +690,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-12 08:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-05-16 17:00</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>40</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -731,35 +745,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-05-19 08:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-05-22 17:00</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -784,35 +800,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-05-09 17:00</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>40</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -837,35 +855,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>2026-05-12 08:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2026-05-16 17:00</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>40</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -890,35 +910,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-06-02 08:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2026-06-06 17:00</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>40</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -943,35 +965,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2026-06-09 08:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2026-06-10 17:00</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>16</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>FAB A</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -996,35 +1020,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2026-05-09 17:00</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>40</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1049,35 +1075,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>2026-05-12 08:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2026-05-15 17:00</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>30</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>GROUPE 1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GROUPE 1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -1102,35 +1130,37 @@
           <t>CPFAE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>2026-05-05 08:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2026-05-08 17:00</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>32</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>FAB B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>GROUPE 2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>SESSION 2026</t>
         </is>
@@ -3878,7 +3908,7 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>Formation, Module (titre), Site, Date début, Date fin, Volume horaire (h), Catégorie, Grade, Groupe, Vague</t>
+          <t>Formation, Module (titre), Site, Bâtiment, Salle, Date début, Date fin, Volume horaire (h), Catégorie, Grade, Groupe, Vague</t>
         </is>
       </c>
     </row>
